--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N26_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.02966212866475</v>
+        <v>12.51732009590802</v>
       </c>
       <c r="D2" t="n">
-        <v>88.95262784201488</v>
+        <v>14.45480202432742</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
